--- a/D_Diverses/WH_calculator.xlsx
+++ b/D_Diverses/WH_calculator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\D_Dokumente\P_Privat\D_Diverses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E45E4B-13DD-4186-B2B4-E5FD0429F43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DAB6D1-268D-46F8-BD24-B5912786D3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{810CD67B-DC38-4B4E-8EC1-A8411912ADDC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{810CD67B-DC38-4B4E-8EC1-A8411912ADDC}"/>
   </bookViews>
   <sheets>
     <sheet name="2000" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="62">
   <si>
     <t>Ahriman</t>
   </si>
@@ -185,24 +185,6 @@
     <t>Forgefiend</t>
   </si>
   <si>
-    <t>Internal Master + 5 Rubric + Eldritch</t>
-  </si>
-  <si>
-    <t>Internal Master + 5 Rubric</t>
-  </si>
-  <si>
-    <t>Tzangors Bow</t>
-  </si>
-  <si>
-    <t>Tzangors</t>
-  </si>
-  <si>
-    <t>Exalted Sorcerer on Disc + 10 rubric + Umbralific</t>
-  </si>
-  <si>
-    <t>Exalted Sorcerer + 10 rubric + Incadeum</t>
-  </si>
-  <si>
     <t>Exalted Sorcerer on Disc + 1aspiring + 1rubric soulReaper + 5rubrics bolters + 3rubric flamers + umbralific cristal</t>
   </si>
   <si>
@@ -216,6 +198,33 @@
   </si>
   <si>
     <t>Exalted Sorcerer on Disc + 1aspiring + 1rubric soulReaper + 5rubrics bolters + 3rubric flamers</t>
+  </si>
+  <si>
+    <t>HQ</t>
+  </si>
+  <si>
+    <t>Exalted Sorcerer + 5 Rubrics with Flamers</t>
+  </si>
+  <si>
+    <t>Exalted Sorcerer on Disc + 10 Rubrics with Flamers and Bolters + Umbralific Cristal</t>
+  </si>
+  <si>
+    <t>Infernal Master + 5 Rubircs with Flamers + Eldritch Vortex</t>
+  </si>
+  <si>
+    <t>Infernal Master + 5 Rubircs with Flamers</t>
+  </si>
+  <si>
+    <t>Backbone</t>
+  </si>
+  <si>
+    <t>Heavy</t>
+  </si>
+  <si>
+    <t>Tzaangors</t>
+  </si>
+  <si>
+    <t>Mission</t>
   </si>
 </sst>
 </file>
@@ -587,16 +596,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CBF4480-DEB2-4CC7-8894-E8DF9C0D5F1B}">
-  <dimension ref="A1:F34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.88671875" customWidth="1"/>
-    <col min="6" max="6" width="49.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="74.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -609,26 +618,29 @@
       <c r="D1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2">
         <f>B2*C2</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -640,10 +652,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -655,10 +670,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="G4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -670,10 +688,13 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="G5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -688,10 +709,13 @@
         <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+      <c r="G6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -706,10 +730,13 @@
         <v>100</v>
       </c>
       <c r="F7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="G7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -724,10 +751,13 @@
         <v>190</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -742,10 +772,13 @@
         <v>435</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -760,40 +793,55 @@
         <v>350</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="G10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11">
         <v>105</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>210</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+      <c r="F11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>190</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>380</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -805,7 +853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -817,7 +865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -829,7 +877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -841,7 +889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -853,7 +901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -865,7 +913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -880,7 +928,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -895,7 +943,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -907,13 +955,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -922,7 +970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -937,22 +985,19 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>22</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
       <c r="C25">
         <v>15</v>
       </c>
       <c r="D25">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -964,7 +1009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -979,13 +1024,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -994,7 +1039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -1006,7 +1051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -1018,7 +1063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -1030,7 +1075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -1042,7 +1087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D34">
         <f>SUM(D2:D33)</f>
         <v>1995</v>
@@ -1056,17 +1101,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B74B60-88FD-400C-A669-AA4CC3F654E7}">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.88671875" customWidth="1"/>
-    <col min="6" max="6" width="49.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="49.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1080,7 +1125,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1101,7 +1146,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1119,7 +1164,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1137,7 +1182,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1155,7 +1200,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1173,7 +1218,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1194,7 +1239,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -1212,7 +1257,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -1233,7 +1278,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1245,7 +1290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -1260,7 +1305,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1275,7 +1320,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1290,7 +1335,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1305,7 +1350,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1317,7 +1362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1329,7 +1374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1341,7 +1386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1356,7 +1401,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -1371,7 +1416,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1386,7 +1431,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1398,7 +1443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -1410,13 +1455,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -1425,7 +1470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -1437,7 +1482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -1449,7 +1494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -1461,7 +1506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -1476,13 +1521,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -1491,7 +1536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -1503,7 +1548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -1515,7 +1560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -1527,7 +1572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -1539,7 +1584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D35">
         <f>SUM(D2:D34)</f>
         <v>1495</v>
@@ -1553,17 +1598,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6F0F84-7EDB-47B1-81FF-28F2994AFF5B}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.88671875" customWidth="1"/>
-    <col min="6" max="6" width="91.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="91.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1577,7 +1622,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1595,7 +1640,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1607,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1622,10 +1667,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1640,7 +1685,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1658,7 +1703,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1676,7 +1721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -1691,7 +1736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -1709,7 +1754,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1721,7 +1766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -1736,7 +1781,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1751,7 +1796,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1766,7 +1811,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1778,7 +1823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1790,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1802,7 +1847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1814,7 +1859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1826,7 +1871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -1838,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1853,7 +1898,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1865,7 +1910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -1877,13 +1922,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -1892,7 +1937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -1904,7 +1949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -1919,7 +1964,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -1931,7 +1976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -1946,13 +1991,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -1961,7 +2006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -1973,7 +2018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -1985,7 +2030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -1997,7 +2042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -2009,7 +2054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D35">
         <f>SUM(D2:D34)</f>
         <v>1500</v>
@@ -2023,17 +2068,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8104D03B-8447-4977-8E53-436B8DE372BD}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.88671875" customWidth="1"/>
-    <col min="6" max="6" width="91.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="91.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -2047,7 +2092,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2065,7 +2110,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2077,10 +2122,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2092,10 +2137,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2110,7 +2155,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2128,7 +2173,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2143,10 +2188,10 @@
         <v>100</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -2161,7 +2206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -2176,7 +2221,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2188,7 +2233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -2203,7 +2248,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2218,7 +2263,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2233,7 +2278,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2248,7 +2293,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2260,7 +2305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2272,7 +2317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2284,7 +2329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2296,7 +2341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -2311,7 +2356,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -2323,7 +2368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -2335,7 +2380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -2347,13 +2392,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -2362,7 +2407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -2374,7 +2419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -2386,7 +2431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -2398,7 +2443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -2410,13 +2455,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -2425,7 +2470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -2437,7 +2482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2449,7 +2494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -2461,7 +2506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -2473,7 +2518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D35">
         <f>SUM(D2:D34)</f>
         <v>1500</v>

--- a/D_Diverses/WH_calculator.xlsx
+++ b/D_Diverses/WH_calculator.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Christoph Bolz\Documents\Privat\div\D_Diverses\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\D_Dokumente\P_Privat\D_Diverses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98759F4-25D7-4BB9-8950-8A002B370547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DAB6D1-268D-46F8-BD24-B5912786D3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{810CD67B-DC38-4B4E-8EC1-A8411912ADDC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{810CD67B-DC38-4B4E-8EC1-A8411912ADDC}"/>
   </bookViews>
   <sheets>
     <sheet name="2000" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="62">
   <si>
     <t>Ahriman</t>
   </si>
@@ -185,24 +185,6 @@
     <t>Forgefiend</t>
   </si>
   <si>
-    <t>Internal Master + 5 Rubric + Eldritch</t>
-  </si>
-  <si>
-    <t>Internal Master + 5 Rubric</t>
-  </si>
-  <si>
-    <t>Tzangors Bow</t>
-  </si>
-  <si>
-    <t>Tzangors</t>
-  </si>
-  <si>
-    <t>Exalted Sorcerer on Disc + 10 rubric + Umbralific</t>
-  </si>
-  <si>
-    <t>Exalted Sorcerer + 10 rubric + Incadeum</t>
-  </si>
-  <si>
     <t>Exalted Sorcerer on Disc + 1aspiring + 1rubric soulReaper + 5rubrics bolters + 3rubric flamers + umbralific cristal</t>
   </si>
   <si>
@@ -216,6 +198,33 @@
   </si>
   <si>
     <t>Exalted Sorcerer on Disc + 1aspiring + 1rubric soulReaper + 5rubrics bolters + 3rubric flamers</t>
+  </si>
+  <si>
+    <t>HQ</t>
+  </si>
+  <si>
+    <t>Exalted Sorcerer + 5 Rubrics with Flamers</t>
+  </si>
+  <si>
+    <t>Exalted Sorcerer on Disc + 10 Rubrics with Flamers and Bolters + Umbralific Cristal</t>
+  </si>
+  <si>
+    <t>Infernal Master + 5 Rubircs with Flamers + Eldritch Vortex</t>
+  </si>
+  <si>
+    <t>Infernal Master + 5 Rubircs with Flamers</t>
+  </si>
+  <si>
+    <t>Backbone</t>
+  </si>
+  <si>
+    <t>Heavy</t>
+  </si>
+  <si>
+    <t>Tzaangors</t>
+  </si>
+  <si>
+    <t>Mission</t>
   </si>
 </sst>
 </file>
@@ -587,16 +596,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CBF4480-DEB2-4CC7-8894-E8DF9C0D5F1B}">
-  <dimension ref="A1:F34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.88671875" customWidth="1"/>
-    <col min="6" max="6" width="49.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="74.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -609,26 +618,29 @@
       <c r="D1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2">
         <f>B2*C2</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -640,10 +652,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -655,10 +670,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="G4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -670,10 +688,13 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="G5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -688,10 +709,13 @@
         <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+      <c r="G6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -706,10 +730,13 @@
         <v>100</v>
       </c>
       <c r="F7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="G7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -717,17 +744,20 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -735,17 +765,20 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>435</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>95</v>
+        <v>435</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -753,119 +786,134 @@
         <v>2</v>
       </c>
       <c r="C10">
-        <v>435</v>
+        <v>175</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>350</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="G10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+      <c r="F11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="C13">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="C14">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="C15">
-        <v>360</v>
+        <v>80</v>
       </c>
       <c r="D15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="C16">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="D16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
       <c r="C17">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="D17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
       <c r="C18">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -873,14 +921,14 @@
         <v>2</v>
       </c>
       <c r="C19">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="D19">
         <f t="shared" si="0"/>
-        <v>170</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -888,35 +936,32 @@
         <v>1</v>
       </c>
       <c r="C20">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D20">
         <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="C21">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="D21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C22">
-        <v>160</v>
-      </c>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -925,7 +970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -940,22 +985,19 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>22</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
       <c r="C25">
         <v>15</v>
       </c>
       <c r="D25">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -967,7 +1009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -982,13 +1024,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -997,7 +1039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -1009,7 +1051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -1021,7 +1063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -1033,7 +1075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -1045,10 +1087,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D34">
         <f>SUM(D2:D33)</f>
-        <v>2240</v>
+        <v>1995</v>
       </c>
     </row>
   </sheetData>
@@ -1059,17 +1101,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B74B60-88FD-400C-A669-AA4CC3F654E7}">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.88671875" customWidth="1"/>
-    <col min="6" max="6" width="49.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="49.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1083,7 +1125,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1104,7 +1146,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1122,7 +1164,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1140,7 +1182,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1158,7 +1200,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1176,7 +1218,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1197,12 +1239,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>47</v>
       </c>
       <c r="C8">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D8">
         <f t="shared" ref="D8" si="1">B8*C8</f>
@@ -1215,7 +1257,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -1236,7 +1278,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1248,7 +1290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -1256,14 +1298,14 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>170</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1271,14 +1313,14 @@
         <v>3</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1293,7 +1335,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1308,7 +1350,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1320,7 +1362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1332,7 +1374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1344,7 +1386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1352,14 +1394,14 @@
         <v>1</v>
       </c>
       <c r="C18">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D18">
         <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -1374,7 +1416,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1389,7 +1431,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1401,7 +1443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -1413,13 +1455,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -1428,7 +1470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -1440,7 +1482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -1452,7 +1494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -1464,7 +1506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -1479,13 +1521,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -1494,7 +1536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -1506,7 +1548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -1518,7 +1560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -1530,7 +1572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -1542,10 +1584,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D35">
         <f>SUM(D2:D34)</f>
-        <v>1470</v>
+        <v>1495</v>
       </c>
     </row>
   </sheetData>
@@ -1556,17 +1598,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6F0F84-7EDB-47B1-81FF-28F2994AFF5B}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.88671875" customWidth="1"/>
-    <col min="6" max="6" width="91.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="91.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1580,7 +1622,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1598,7 +1640,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1610,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1625,10 +1667,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1643,7 +1685,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1661,7 +1703,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1679,12 +1721,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>47</v>
       </c>
       <c r="C8">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -1694,7 +1736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -1712,7 +1754,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1724,7 +1766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -1732,14 +1774,14 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1747,14 +1789,14 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1769,7 +1811,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1781,7 +1823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1793,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1805,7 +1847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1817,19 +1859,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
       <c r="C18">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -1841,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1856,7 +1898,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1868,7 +1910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -1880,13 +1922,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -1895,7 +1937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -1907,7 +1949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -1922,7 +1964,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -1934,7 +1976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -1949,13 +1991,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -1964,7 +2006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -1976,7 +2018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -1988,7 +2030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -2000,7 +2042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -2012,10 +2054,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D35">
         <f>SUM(D2:D34)</f>
-        <v>1480</v>
+        <v>1500</v>
       </c>
     </row>
   </sheetData>
@@ -2026,17 +2068,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8104D03B-8447-4977-8E53-436B8DE372BD}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.88671875" customWidth="1"/>
-    <col min="6" max="6" width="91.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="91.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -2050,7 +2092,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2068,7 +2110,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2080,10 +2122,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2095,10 +2137,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2113,7 +2155,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2131,7 +2173,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2146,15 +2188,15 @@
         <v>100</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>47</v>
       </c>
       <c r="C8">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -2164,7 +2206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -2179,7 +2221,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2191,7 +2233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -2199,14 +2241,14 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>170</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2214,14 +2256,14 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2236,7 +2278,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2251,7 +2293,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2263,7 +2305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2275,7 +2317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2287,19 +2329,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
       <c r="C18">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -2314,7 +2356,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -2326,7 +2368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -2338,7 +2380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -2350,13 +2392,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -2365,7 +2407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -2377,7 +2419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -2389,7 +2431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -2401,7 +2443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -2413,13 +2455,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -2428,7 +2470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -2440,7 +2482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2452,7 +2494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -2464,7 +2506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -2476,10 +2518,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D35">
         <f>SUM(D2:D34)</f>
-        <v>1485</v>
+        <v>1500</v>
       </c>
     </row>
   </sheetData>
